--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260702.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260702.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>18.39%</t>
+          <t>18.23%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.27%</t>
+          <t>7.17%</t>
         </is>
       </c>
     </row>
@@ -660,117 +660,117 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.57%</t>
+          <t>6.13%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>8,960,000</t>
+          <t>3,450,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.34%</t>
+          <t>5.46%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>3,450,000</t>
+          <t>8,960,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.18%</t>
+          <t>5.07%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>38,800,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.23%</t>
+          <t>4.19%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1,140,000</t>
+          <t>38,800,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>4.11%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>940,000</t>
+          <t>1,140,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>3.73%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.60%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
@@ -858,51 +858,51 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>6,440,000</t>
+          <t>5,600,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>5,300,000</t>
+          <t>6,440,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
@@ -924,90 +924,90 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,700,000</t>
+          <t>830,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>3,217,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>830,000</t>
+          <t>1,240,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,240,000</t>
+          <t>3,217,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,66 +1019,66 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,560,000</t>
+          <t>480,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,560,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1122,51 +1122,51 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>7,550,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>7,550,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1210,156 +1210,156 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>5,500,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>570,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>570,000</t>
+          <t>795,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>795,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,198 +1371,198 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>1,560,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,560,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>1,010,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>166,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,010,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>166,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
@@ -1623,24 +1623,24 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>5,929,354,917</t>
+          <t>5,213,664,048</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,748,522,183</t>
+          <t>1,733,755,327</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
